--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-01-2026.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.55</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>£40.35</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£26.89</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>£52.32</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>£1126.15</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
